--- a/virtual-physics-lab/app/dl/ASRJC_Q2_compound_pendulum.xlsx
+++ b/virtual-physics-lab/app/dl/ASRJC_Q2_compound_pendulum.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,106 +696,106 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>32.12</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>32.06</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>31.4</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>31.36</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>30.74</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>30.8</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>30.48</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>30.51</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>30.69</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>30.77</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>31.64</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>31.52</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>33.68</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>33.84</v>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -889,38 +893,38 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>32.12</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>32.06</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>(B6+C6)/40</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>(50.0-A6)/100</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>D6^2*E6</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <f>E6^2</f>
         <v/>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>M = gradient</t>
         </is>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="8">
         <f>SLOPE(F6:F12,G6:G12)</f>
         <v/>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>s² m⁻¹</t>
         </is>
@@ -930,38 +934,38 @@
       <c r="A7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>31.4</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>31.36</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>(B7+C7)/40</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>(50.0-A7)/100</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>D7^2*E7</f>
         <v/>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <f>E7^2</f>
         <v/>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>b = √(intercept/M)</t>
         </is>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="8">
         <f>SQRT(INTERCEPT(F6:F12,G6:G12)/SLOPE(F6:F12,G6:G12))</f>
         <v/>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -971,38 +975,38 @@
       <c r="A8" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>30.74</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>30.8</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>(B8+C8)/40</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>(50.0-A8)/100</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>D8^2*E8</f>
         <v/>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f>E8^2</f>
         <v/>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>g = 4π²/M</t>
         </is>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="8">
         <f>4*PI()^2/SLOPE(F6:F12,G6:G12)</f>
         <v/>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>m s⁻²</t>
         </is>
@@ -1012,25 +1016,25 @@
       <c r="A9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>30.48</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>30.51</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>(B9+C9)/40</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>(50.0-A9)/100</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>D9^2*E9</f>
         <v/>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f>E9^2</f>
         <v/>
       </c>
@@ -1039,25 +1043,25 @@
       <c r="A10" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>30.69</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>30.77</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>(B10+C10)/40</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>(50.0-A10)/100</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>D10^2*E10</f>
         <v/>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <f>E10^2</f>
         <v/>
       </c>
@@ -1066,25 +1070,25 @@
       <c r="A11" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>31.64</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>31.52</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>(B11+C11)/40</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>(50.0-A11)/100</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>D11^2*E11</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>E11^2</f>
         <v/>
       </c>
@@ -1093,25 +1097,25 @@
       <c r="A12" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>33.68</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>33.84</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>(B12+C12)/40</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>(50.0-A12)/100</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f>D12^2*E12</f>
         <v/>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <f>E12^2</f>
         <v/>
       </c>
